--- a/光伏配储项目/电价数据/2026/黄茅海站.xlsx
+++ b/光伏配储项目/电价数据/2026/黄茅海站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.55424</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38009</v>
+      </c>
+      <c r="C117" t="n">
+        <v>1.74026</v>
+      </c>
+      <c r="D117" t="n">
+        <v>1.18767</v>
+      </c>
+      <c r="E117" t="n">
+        <v>1.19723</v>
+      </c>
+      <c r="F117" t="n">
+        <v>1.23722</v>
+      </c>
+      <c r="G117" t="n">
+        <v>1.25282</v>
+      </c>
+      <c r="H117" t="n">
+        <v>1.18697</v>
+      </c>
+      <c r="I117" t="n">
+        <v>1.18696</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.44043</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.7351799999999999</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.7881699999999999</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.72077</v>
+      </c>
+      <c r="N117" t="n">
+        <v>1.18692</v>
+      </c>
+      <c r="O117" t="n">
+        <v>1.18681</v>
+      </c>
+      <c r="P117" t="n">
+        <v>1.18698</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.71405</v>
+      </c>
+      <c r="R117" t="n">
+        <v>1.18696</v>
+      </c>
+      <c r="S117" t="n">
+        <v>1.18697</v>
+      </c>
+      <c r="T117" t="n">
+        <v>1.18697</v>
+      </c>
+      <c r="U117" t="n">
+        <v>1.18698</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.76991</v>
+      </c>
+      <c r="W117" t="n">
+        <v>1.18697</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39494</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.7430099999999999</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>1.18697</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>1.19096</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.7877000000000001</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>1.21536</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>1.29596</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.32442</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.34496</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.32885</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.34054</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.40482</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.88798</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.69578</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.6901499999999999</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.31734</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.47095</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.75818</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.78138</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.4043</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.39366</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>1.0502</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>1.03943</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>1.1311</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.7605</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.32584</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.72323</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.50873</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.41074</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.4070299999999999</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.41132</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.79311</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.98663</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>1.34915</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.53126</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.78538</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.43018</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.79364</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.76667</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.96228</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.9261699999999999</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>1.07756</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>1.35401</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>1.20909</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>1.24773</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.74907</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.25541</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>1.1972</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>1.10637</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>1.25651</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>1.55047</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>1.27102</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.28425</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>1.50057</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>1.34119</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>1.2601</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>1.44048</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>1.38097</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>1.31318</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.81814</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47924</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.41065</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.4127</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.4219</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32993</v>
+      </c>
+      <c r="C118" t="n">
+        <v>1.19268</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>1.04625</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>1.18293</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.53623</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5226499999999999</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50627</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.5162899999999999</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.81072</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.71294</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.78504</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.69155</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38091</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39206</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.34562</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.6831</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.8066</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.74978</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.74997</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.74998</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.73094</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.79365</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>1.10137</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>1.46322</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>1.03645</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.789</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.68262</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.74866</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.65023</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.6502899999999999</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.9622999999999999</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>1.17522</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.80052</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>1.13154</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>1.06066</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>1.02308</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.72751</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.55583</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.5786699999999999</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.6990299999999999</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.35212</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>1.20067</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>1.26618</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>1.51615</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.31667</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>1.19619</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>1.67017</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>1.09278</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.8460800000000001</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>1.2793</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>1.17014</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>1.29721</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.31675</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.6262300000000001</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.65287</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.57614</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.62738</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>1.21131</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>1.20333</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>1.21095</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>1.2041</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>1.00213</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>1.18365</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.19875</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.19537</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.67598</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>1.19857</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.20795</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.26493</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.56294</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.47899</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.20376</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>1.50643</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>1.26641</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.7564299999999999</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.7638400000000001</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.91411</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44059</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43462</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.41383</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.3388</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.3772</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35426</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33341</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32156</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.75226</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.94899</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.9010199999999999</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.65266</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.7506900000000001</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.65047</v>
+      </c>
+      <c r="I119" t="n">
+        <v>1.5898</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.95026</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.94131</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.89139</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.7691</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.95041</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.74661</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.9501900000000001</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.6502100000000001</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37083</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35297</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.35831</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.34822</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36269</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35588</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.37974</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39645</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.75001</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.65018</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.75018</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.7487699999999999</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.70917</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.74859</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.7479600000000001</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.6589299999999999</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.7080299999999999</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.83985</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>1.12033</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.8819199999999999</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.7674800000000001</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.71439</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.6095499999999999</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.3078</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.31738</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.30098</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.6414500000000001</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.42646</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.74593</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>1.18475</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>1.5618</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.69713</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>1.19352</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>1.67237</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>1.19592</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>1.19986</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.80929</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.97502</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>1.20172</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>1.20178</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.90855</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.56335</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.4147</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.47719</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.6799400000000001</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>1.18911</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>1.05375</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>1.20022</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>1.44119</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>1.28343</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>1.19923</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>1.22355</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>1.21452</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>1.44902</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>1.29325</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>1.30825</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>1.67029</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>1.21696</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>1.21487</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>1.07122</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>1.10368</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>1.12454</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>1.11061</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>1.23989</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>1.19569</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>1.28318</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>1.02438</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.7702599999999999</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.72764</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.53877</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.41308</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34314</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31994</v>
+      </c>
+      <c r="C120" t="n">
+        <v>1.19522</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.9326</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.91603</v>
+      </c>
+      <c r="F120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.88775</v>
+      </c>
+      <c r="H120" t="n">
+        <v>1.0571</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.73914</v>
+      </c>
+      <c r="J120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="K120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.8999400000000001</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.76906</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.97587</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.94886</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.88437</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.74921</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.74946</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.6467999999999999</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.54977</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33524</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33379</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.32521</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.53143</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.34566</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.76908</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.7493</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.89986</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.74864</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.69238</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.64986</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.55103</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.34575</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.68743</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.72456</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.94229</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>1.19655</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>1.33991</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.8633099999999999</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>1.58225</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>1.67252</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.91325</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.8949600000000001</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>1.1902</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>1.44748</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>1.77929</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.98813</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>1.24874</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.70986</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>1.11817</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.53063</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.49279</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.67026</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>1.02626</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>1.12771</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>1.26622</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>1.1998</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>1.10084</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>1.01606</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>1.03531</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.99926</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>1.29685</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>1.4778</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.81463</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>1.38317</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>1.23463</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.86624</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>1.10708</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>1.13443</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>1.18984</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>1.28647</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>1.34685</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>1.18967</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>1.30031</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>1.20423</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>1.19193</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>1.1861</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>1.21683</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>1.22888</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>1.21457</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>1.19162</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>1.19003</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.74313</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.53176</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.33555</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.7472799999999999</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.33251</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.33205</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.34073</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.34121</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.32199</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.7501</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.49975</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.40629</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36483</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34515</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.34336</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.34355</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.35417</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.34364</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.34306</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.34265</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.34287</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.34279</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.34269</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.34053</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.34108</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.34098</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.34081</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.34102</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.34111</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.34116</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.34117</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.34078</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.3404700000000001</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.33735</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.33509</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33978</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.33995</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.33423</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.3389</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.48473</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.51127</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.5306000000000001</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.34021</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.40593</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.31947</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.46483</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.34483</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.43343</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.46279</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.7286</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.862</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.6253300000000001</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.7135499999999999</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.34598</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.73899</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.33832</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.85956</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.71713</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.33935</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.5602200000000001</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.5592699999999999</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.5478500000000001</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.60254</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.47889</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.10219</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.33243</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.31011</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.2933</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.28628</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.31556</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.33442</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>0.33625</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.55624</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.49203</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.52355</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.46911</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.65004</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.51246</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.49202</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.40322</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.49246</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.49571</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.60873</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.40642</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.51349</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.5124299999999999</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.40946</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.49152</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.35544</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.41099</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.39954</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39844</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.40988</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46754</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.38188</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39643</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40002</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.40546</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35809</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34469</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35529</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.3443</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="C122" t="n">
+        <v>1.21935</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.9970399999999999</v>
+      </c>
+      <c r="E122" t="n">
+        <v>1.01214</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.5994400000000001</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.7967000000000001</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.80088</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.72887</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.80048</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.36442</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.8018999999999999</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.80175</v>
+      </c>
+      <c r="N122" t="n">
+        <v>1.18682</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.8012</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.80106</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.80174</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.80228</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.34189</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33995</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.80228</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.3377</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.33847</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.33771</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33532</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.3388</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35003</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35201</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34245</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31602</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.27842</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.07493999999999999</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04659000000000001</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>0.31129</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04281</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04375</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04318</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.04177</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.04664</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.27512</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.08405</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.04341</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.29674</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.13121</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04294</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04452</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.0466</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04647999999999999</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04486</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>0.0036</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.0423</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04627000000000001</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04506</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.04233</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>0.30796</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04617</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04477</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04545</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04346</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.30587</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.3093399999999999</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>0.26887</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>0.28619</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>0.2942</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>0.29759</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.36065</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.39323</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.43032</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.3654</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.36602</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.35896</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.35869</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.44865</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.79834</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.80061</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.36381</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.39434</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.39058</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.36475</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.3945</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.7999400000000001</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.8011900000000001</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.80103</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.35914</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.34129</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.36792</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.39776</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.36506</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34551</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.3675</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36598</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33457</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33127</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.77044</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.70131</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.4055299999999999</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.3449</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32179</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.31718</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.32099</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.31405</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.3122799999999999</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.27877</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.30825</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.30676</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.31042</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.30578</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.30439</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.30837</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.29127</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.28752</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17179</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14841</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.16014</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15938</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23743</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21479</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.29379</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.27502</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.30819</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.31134</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.32028</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.31825</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.31217</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.31567</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.31552</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.30461</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.32224</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32355</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.32923</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.3367</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.389</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.7649</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.90188</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.69411</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.6681699999999999</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.68576</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.76846</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.96696</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.41287</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.36424</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.48413</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.74666</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.74959</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.91352</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.5481200000000001</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.48519</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.4569</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.09423000000000001</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29704</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.32265</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.37809</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.3034</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.38137</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.74534</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.7506799999999999</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.6549299999999999</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.6143999999999999</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.48068</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.74011</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79104</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.79115</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.6109</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.75452</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>1.03098</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>1.43166</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.8613999999999999</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>1.46128</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>1.34823</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.81248</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>1.40671</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>1.06537</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>1.42707</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.78832</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.46565</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.78734</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.80104</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5303600000000001</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.78769</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.78555</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87858</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87914</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.50259</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.41209</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.41215</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.46079</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.21926</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87937</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55135</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.6393799999999999</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.5414099999999999</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.8135399999999999</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.7991</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.7998999999999999</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.79932</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.79959</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.70492</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.79967</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.80028</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.66632</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.6501699999999999</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.67762</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38636</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41494</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43395</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34402</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.8011200000000001</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.8029500000000001</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.79864</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.7984</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.8001</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.79995</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.8001699999999999</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.76323</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.6682899999999999</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.79759</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.6502</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.60021</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.43742</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59623</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.5648200000000001</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>1.07799</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.64759</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.50914</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.57702</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>1.59678</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>1.00964</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>1.34252</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.31111</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>1.27306</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.5611799999999999</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.80023</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.57656</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.65652</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.55852</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.98976</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.78749</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.73619</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.65146</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.58365</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>1.02214</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>1.16097</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.5704199999999999</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.75726</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.7517</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.7969299999999999</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.70089</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.75088</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.9000199999999999</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.74999</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.75001</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.6103099999999999</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.59221</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.75088</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.79772</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.7984199999999999</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.79804</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.7948099999999999</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.78496</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.7960199999999999</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.80247</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.79552</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.8024600000000001</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.8000900000000001</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.7958999999999999</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.7961699999999999</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.7978099999999999</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.79657</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.7988</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.8013899999999999</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.81004</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.80053</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.79955</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.80047</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.8010499999999999</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.80147</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.6656599999999999</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32928</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.95612</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36058</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.7500800000000001</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.95312</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.89958</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.95259</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.7839400000000001</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.78585</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.70139</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.7509</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.37524</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.35227</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.36415</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35926</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34579</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.65015</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50007</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.3572</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38768</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34357</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35092</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.3553</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37063</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35772</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36285</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31632</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31347</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33246</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.6646</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.41127</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.53331</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.63018</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.7506900000000001</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.90076</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>1.15391</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.94176</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.56084</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>1.12596</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.8684400000000001</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.97689</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.88589</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.65437</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.8357899999999999</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>1.09771</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.34554</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.7473</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.53427</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.43819</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.38195</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.37802</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.90451</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>1.2181</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.9533700000000001</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>1.23684</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.80814</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.8393400000000001</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.9500700000000001</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.76089</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.33472</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.40844</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.39354</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.35238</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.37646</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.34552</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32842</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.47809</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.39571</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.38154</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.36538</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.4449</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.38337</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.34448</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.37116</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.35044</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.39765</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.5006</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.4325</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.42046</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.41592</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44783</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.34464</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42044</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35897</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40171</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40044</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59675</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="C126" t="n">
+        <v>1.20062</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.51805</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.70359</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.79534</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.64979</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.5836399999999999</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45044</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45034</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50049</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.4399</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43746</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41504</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42352</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.5005500000000001</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43408</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41293</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43413</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39041</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42803</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45041</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39631</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.4235</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43412</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40027</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42354</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.3966</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.4025</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.80363</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.43923</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.7704800000000001</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>1.1911</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.93508</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.65818</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.71554</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>1.57875</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.35144</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>1.17769</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>1.6357</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.92291</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.6001299999999999</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>1.79569</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>1.54638</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>1.46978</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>1.43779</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>1.2191</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>1.54235</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.3456</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.61665</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.8726799999999999</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>1.52929</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.76434</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>1.09699</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>1.0958</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.96328</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.99646</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.9503400000000001</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>1.18703</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>1.1855</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.88914</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>1.18552</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>1.63144</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.9978899999999999</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>1.04182</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>1.18554</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.97833</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>1.01926</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>1.60846</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.9507899999999999</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>1.00768</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>1.11492</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.91218</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.89981</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>1.12475</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>1.61367</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.9866</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>1.02404</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.7587</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38619</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36888</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33384</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.3406</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32945</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.34359</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31897</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.8996499999999999</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.7495499999999999</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.74976</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.34556</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.34569</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.3435</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.34573</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32621</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.34359</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.34341</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.31014</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.34416</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.34288</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.34312</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.34328</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.34333</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.34392</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.34364</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.34308</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.34145</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.34313</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.34327</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.70384</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32507</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.34995</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37499</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33881</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.59996</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33219</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33457</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.7262000000000001</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33721</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.3941</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.34249</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.95784</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.7585</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.70682</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.75429</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.70445</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.31486</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.75428</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>0.8358</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0.7275</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.31117</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.90422</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.7696799999999999</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>1.16878</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>1.47433</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.77176</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.77395</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.7757000000000001</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.7115900000000001</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.71469</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.77561</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.9077200000000001</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.91631</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.7717200000000001</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.65346</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.6470499999999999</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.65683</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.65911</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.3722200000000001</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.70002</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.37952</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.40323</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.36158</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.4054</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34364</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.37994</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.3466</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.40024</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.36071</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38491</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.69999</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.69989</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39356</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40188</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39772</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.45674</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.43992</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.4392799999999999</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.4442</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44427</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.69978</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.70287</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.69982</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.3916</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35974</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.36039</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34804</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34934</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.3397</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.61211</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.54987</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46869</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42386</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41593</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37014</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38108</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.38021</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.6001299999999999</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.90008</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.80031</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.80037</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.8002999999999999</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.81921</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.70033</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.74537</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.60026</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35526</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34578</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.50024</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.60025</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.50025</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.77119</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.8102999999999999</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.80031</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.7702599999999999</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.70016</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.7001000000000001</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.6525700000000001</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34593</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32934</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34866</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.35154</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.3755</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29475</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31696</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.3169</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.3335</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29398</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.32085</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.55863</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.29407</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.33223</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.3574</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.32231</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.28219</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.26677</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30023</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30818</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31698</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.30662</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.47333</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.30696</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.33138</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.31458</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.3334</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.32931</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.33551</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.36549</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.31412</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.38392</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.48712</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.70543</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.6058300000000001</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.62659</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.79688</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.80011</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.83788</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.8001</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.45041</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.39628</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.42853</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.7001799999999999</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.78791</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.7811699999999999</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>1.11894</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.6857000000000001</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.5412</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.43858</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.42936</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.39696</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.37968</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41952</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.39203</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.49693</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.44723</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.41391</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.42593</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38036</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38532</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36025</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36608</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.41871</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37069</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.5658300000000001</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38051</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35277</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34951</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36025</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35177</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.3478</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34581</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.64632</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.6434299999999999</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.6463300000000001</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.60058</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.76903</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.50163</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.6005499999999999</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.50057</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.3454700000000001</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.34645</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.59985</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.66976</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.76847</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.6928300000000001</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.766</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>1.13459</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>1.47688</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.34605</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.41499</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>1.30789</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>1.00121</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.98993</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.99151</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>1.56141</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>1.55217</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.9438500000000001</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.82838</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>1.79171</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>1.01063</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>1.77572</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>1.65627</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>1.649</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>1.71631</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.7968999999999999</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>1.29459</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.32849</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.7694500000000001</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>1.35734</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.49378</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>1.16547</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.9927999999999999</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>1.65846</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>1.63171</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>1.66534</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>1.67871</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>1.67378</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>1.45556</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>1.63571</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>1.06334</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>1.30748</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>1.67588</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.7899700000000001</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.8901699999999999</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.70548</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>1.71325</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>1.72141</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>1.64031</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>1.7557</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>1.01904</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>1.12843</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.69931</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>1.70775</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>1.70153</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>1.78115</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>1.09884</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>1.04025</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>1.63884</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.8204600000000001</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.6718</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.46501</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>1.27071</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.6512</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.3458</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.76619</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.6416499999999999</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.6750499999999999</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.34638</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.34486</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.33381</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.63607</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.78637</v>
+      </c>
+      <c r="E130" t="n">
+        <v>1.37215</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.6618999999999999</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.7686799999999999</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.34571</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.39241</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.3553</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.67574</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.34643</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.64842</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.8059299999999999</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.7694800000000001</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.7699</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.66704</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.34705</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.34687</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.3468</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.34466</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.34454</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.3425</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.34301</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.62737</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.34356</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34597</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34076</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34573</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.34042</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33875</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.33583</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.35124</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.34624</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.39817</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.40264</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.34492</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.42693</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.75375</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.49542</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.51362</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.52212</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.33808</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.29797</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.34211</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34151</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.30128</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32669</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28471</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.3384</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.33974</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32321</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.33913</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32849</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33348</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.34422</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.34365</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.34154</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.32795</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.34468</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.33614</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.40798</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.45344</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.92986</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>1.0749</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>1.18949</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.80004</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.76161</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.44963</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.3942</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.45721</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.50007</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.50017</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.45075</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.49168</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.3677</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.36162</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.36793</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.36254</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37323</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36208</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39307</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38554</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37163</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.4029700000000001</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.37995</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.36956</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36098</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34937</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34929</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.3395899999999999</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35133</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.35545</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35551</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35138</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35084</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34941</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34626</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.38974</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34705</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.34969</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33704</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.34285</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.34227</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.36932</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.34232</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.34224</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.34237</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33964</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34504</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.3359</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34948</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34948</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33634</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.34267</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34855</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.4059</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.34548</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.40592</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.30055</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.34469</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.34551</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.6252799999999999</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.42029</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.3436</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.38896</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.34634</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.34404</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.34223</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32582</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.34224</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.3188</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.39073</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.34122</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.45069</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.7533300000000001</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.42792</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.51807</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>1.70199</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.49856</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.40688</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.42016</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.4285</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.35447</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.34373</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34561</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.42289</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.5660499999999999</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.38967</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35462</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.4265</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.45524</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35241</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.4016</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34724</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36031</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.36025</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36228</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.35022</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.6694199999999999</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.45032</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.45185</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38358</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.43036</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40911</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.38577</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.38516</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.65181</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.83158</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.47208</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.40269</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45941</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39339</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35068</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35095</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35959</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33989</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34479</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.34612</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.70788</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.6729299999999999</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.66801</v>
+      </c>
+      <c r="F132" t="n">
+        <v>1.26613</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.6563099999999999</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.5758799999999999</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.5350499999999999</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.4617</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.49035</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.459</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35359</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36064</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36081</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35681</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35236</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37086</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35879</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35651</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37949</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36587</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.37991</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35649</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35113</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35182</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35817</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34974</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32989</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.37694</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.43883</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.49971</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.4183</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.49295</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.7598200000000001</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.34563</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.34533</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.36046</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.76632</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.33165</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.34561</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.34381</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.2785899999999999</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.33829</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.48296</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.33792</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.34305</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.34016</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.39384</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.5299199999999999</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.50013</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.35102</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.36049</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.48454</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.50005</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.50032</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.50025</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.4505</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.50042</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>1.48222</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>1.44283</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.4874</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.4939</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.4887</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.36918</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.48977</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.49556</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.49019</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.5405</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.54089</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.54191</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.53155</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.5409299999999999</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.5416799999999999</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.49231</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.68471</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.5006499999999999</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.92541</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.5530700000000001</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.9469099999999999</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>1.00703</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>1.32173</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>1.70768</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.72705</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.716</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.79765</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.61482</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36731</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36016</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.3454</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.7601100000000001</v>
+      </c>
+      <c r="D133" t="n">
+        <v>1.41283</v>
+      </c>
+      <c r="E133" t="n">
+        <v>1.7508</v>
+      </c>
+      <c r="F133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.41947</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.42772</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.70202</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.95073</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.9395800000000001</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.7148099999999999</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.69712</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.87351</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.88928</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.8958200000000001</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.72113</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.91762</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.7189099999999999</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.8879900000000001</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.65097</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.58035</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.58417</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.58413</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.65283</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.47903</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.57968</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.46952</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.7662</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.62579</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.57985</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.87818</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.6596599999999999</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>1.11024</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>1.50853</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>1.60554</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>1.39072</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>1.5435</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.79879</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.9243899999999999</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.7615599999999999</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.72629</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>1.36024</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>1.36134</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>1.39783</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>1.62001</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>1.54139</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>1.20958</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>1.11953</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.55292</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.90361</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.50074</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.50098</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.4977200000000001</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.50071</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.5003</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.50045</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.5002</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.5125599999999999</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.49949</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.60907</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.52332</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.59097</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.55044</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.5016</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.52555</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.6208400000000001</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.79811</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.9627899999999999</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>1.08152</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.9479299999999999</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>1.30454</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>1.2397</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>1.23214</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>1.11264</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>1.43584</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>1.04148</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.9790800000000001</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.91239</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.44874</v>
+      </c>
+      <c r="C134" t="n">
+        <v>1.34695</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.6988</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.49859</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.5823200000000001</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.47688</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42656</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44839</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41786</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.40085</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.45773</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39936</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40707</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39868</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38858</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37995</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.3749</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35688</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37684</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37126</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36021</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38661</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39026</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.3796</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36649</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36138</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35512</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37963</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.44965</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.48772</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.40529</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.53199</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39428</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38661</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35164</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.3685</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.53479</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.55083</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.5509299999999999</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.56092</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.9556399999999999</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.8774</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>1.00978</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.90279</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.49556</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.50078</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.5004999999999999</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.50017</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.5049</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.50369</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.50506</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.50283</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.50596</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.42749</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.50192</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.23502</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.34275</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.32513</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32102</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35264</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.37363</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.3503500000000001</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.42947</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.48244</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.46293</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.5069</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.51097</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.46035</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.36357</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.41266</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.43327</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.5431900000000001</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.52118</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.55614</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38461</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.38768</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.4060299999999999</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40312</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34406</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.36536</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37801</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.39931</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37949</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35508</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39964</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38196</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37501</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.3603</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39386</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37904</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36413</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.3312</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.50054</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.49993</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.50078</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.50045</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.5126799999999999</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.44614</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.42068</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37699</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.41271</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35617</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35984</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.3513</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.3574</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34746</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.39942</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34856</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.39971</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.34392</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33974</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.3404</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33549</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.34049</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33093</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33051</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.3376</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.33767</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.38109</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.34298</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.34114</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.33977</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.32961</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.4201</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.34772</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.33779</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.33994</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.34607</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.35256</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.42075</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.34575</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.34305</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.33878</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.43635</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.38374</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.34879</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.50083</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.32582</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04337</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.36755</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.34271</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.32706</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.34244</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.33099</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.3430299999999999</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.46296</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.33282</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.32311</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.3104</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.30558</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.32578</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.4501</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.29945</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.36079</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.37665</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.36138</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.41294</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34654</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.44644</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.49622</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.48394</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.44983</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.40019</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.46387</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.45063</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.46495</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.34452</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.50092</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.39281</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.45008</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.42537</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.39847</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.41264</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.3771600000000001</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.46139</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.4203</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.46927</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.69992</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.66222</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.6669299999999999</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.6853400000000001</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.64659</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.50024</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.44993</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.40027</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.39981</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.34596</v>
+      </c>
+      <c r="C136" t="n">
+        <v>1.0527</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.49865</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.6995399999999999</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.49993</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.49994</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.62817</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.62183</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.61676</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.6164400000000001</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.34445</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.34411</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.34395</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.3441</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.34462</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.34481</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.3442</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.34422</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.34208</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.34426</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.34374</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.34427</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.34422</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.34441</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.34381</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.34439</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.34423</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.37241</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.38342</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.23461</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.30765</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.27313</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.38881</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.38843</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.34557</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>0.32621</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.30051</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.30637</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>0.34267</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>0.31627</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>0.15431</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>0.73788</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>0.21558</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>0.38769</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>0.30167</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>0.27334</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>0.1412</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.34268</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>0.34628</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>0.35435</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.69977</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.5681799999999999</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>0.30631</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>0.32023</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>0.30633</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>0.29033</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>0.30772</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>0.32223</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>0.38767</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.37513</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.34554</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.39204</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.76874</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.36665</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.39284</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.3548</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.36745</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.38316</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.40011</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.37219</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.40016</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.38304</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.45009</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.45019</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.45018</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.40022</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.3932</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.38315</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.39332</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.38269</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.42906</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.80879</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.38377</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.46815</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.39332</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.38941</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.38938</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.38612</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.4028</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.37111</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.49076</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.31035</v>
+      </c>
+      <c r="C137" t="n">
+        <v>1.1034</v>
+      </c>
+      <c r="D137" t="n">
+        <v>1.38604</v>
+      </c>
+      <c r="E137" t="n">
+        <v>1.19824</v>
+      </c>
+      <c r="F137" t="n">
+        <v>1.08753</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.5261399999999999</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.76114</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.76089</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.51554</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.41794</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.42963</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.42733</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.40943</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.41654</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.39604</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.38831</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.44547</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.55969</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.36045</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.42762</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.38908</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.44509</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.6966599999999999</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>1.30111</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.42611</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.7678200000000001</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.80441</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.45537</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.40368</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.76063</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.41261</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.52964</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>1.48043</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>1.48378</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>1.24436</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>1.08871</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.9871799999999999</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.5505599999999999</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.6367200000000001</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.55192</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.38912</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.49804</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.55063</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.55055</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.55006</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.54967</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.39689</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.23682</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.36248</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.5541699999999999</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.5514600000000001</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.5505599999999999</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.45291</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.32227</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.49854</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.5508200000000001</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.55152</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.5502</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.55061</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.55036</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.8380599999999999</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.6090099999999999</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.5502100000000001</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.61151</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.7877999999999999</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.63746</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.88624</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.60025</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.6003500000000001</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.55032</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.65125</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.62498</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.55023</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.8214199999999999</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>1.16811</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>1.17292</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.8471799999999999</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.48765</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>1.21501</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>1.11858</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>1.17597</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>1.16831</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>1.13576</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>1.04513</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>1.0262</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>1.03535</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>1.54921</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>1.36533</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>1.05895</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.4107</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.38159</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.76039</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.39003</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.34554</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.3302</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.5506</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.54922</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.5528999999999999</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.54888</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.54841</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.55069</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.47092</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.46041</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.40813</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.42955</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.42021</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.35859</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.37101</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.35527</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34822</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.38701</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.38383</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.36873</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.36062</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.35225</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.36195</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.38358</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.42328</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.40586</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.42779</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.55132</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.5500499999999999</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.55213</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.54312</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.45279</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.4819</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.50029</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.55001</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.54665</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.55311</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.5432100000000001</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.54512</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.5334500000000001</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.7503</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>1.74505</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.54752</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.5419400000000001</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.54991</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.5495800000000001</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.54947</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.54974</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.48008</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.28855</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.48467</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.34874</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.55004</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.5505399999999999</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.54701</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.55035</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.55003</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.55045</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.55115</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.55023</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.50012</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.50036</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.48303</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.5002099999999999</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.48265</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.50044</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.5501699999999999</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.55031</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.55014</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.49848</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.51439</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.40355</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.40038</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.38458</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.42361</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.5009100000000001</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.55013</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.55014</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.55032</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.55144</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.5508</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.55111</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.53989</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.54949</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.55033</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.55202</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.54904</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.4973</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.51223</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.49962</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.5355800000000001</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.39201</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.39953</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.34969</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.34538</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.34454</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.37038</v>
+      </c>
+      <c r="D139" t="n">
+        <v>1.06357</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.76754</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.77523</v>
+      </c>
+      <c r="G139" t="n">
+        <v>1.19963</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.76732</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.50024</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.42031</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.40024</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.42018</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.42025</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.35826</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.39341</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.35491</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.35391</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.37966</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.3649</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.36321</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.35317</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34652</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.35415</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.3505</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.36164</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.34348</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36915</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.36236</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.38748</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35943</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.63017</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.5900599999999999</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.42753</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.64275</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>1.03189</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>1.21699</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.80061</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>1.71608</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.93428</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.55032</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.54998</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.55027</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.55016</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.55026</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.5539500000000001</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.52508</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.9124500000000001</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.66273</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.47968</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>1.32381</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.52949</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.50018</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.41967</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.41983</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>1.31897</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>1.17208</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.50024</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.80016</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.55018</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.5499400000000001</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.54962</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>1.11175</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>1.71388</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.6865800000000001</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.54348</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.53525</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.6979299999999999</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.6316799999999999</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.7426699999999999</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.51157</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.55188</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.34204</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.29635</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.31033</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.54601</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.35098</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.32088</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.32209</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.32293</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.7072999999999999</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.42434</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.69047</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.54883</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.40169</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.45852</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.6928</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38012</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.74172</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.70069</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37271</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.36323</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.3687</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.7612000000000001</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.40113</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40117</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39181</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38075</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37556</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37443</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37865</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37732</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36917</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36693</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36154</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35979</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35587</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35619</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35107</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34723</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35016</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36016</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37105</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.39962</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.3757799999999999</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36964</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.36465</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.40372</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.38904</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.71088</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.46579</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.75039</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.5244500000000001</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.51097</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.44385</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>1.02569</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.9234</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>1.03571</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.93377</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>1.04354</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>1.02637</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>1.02655</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.3151</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>1.39014</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>1.09653</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>1.31601</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.67328</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.38971</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.35981</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.6816</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.3574</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.62542</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.7377400000000001</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.72276</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>1.02297</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>1.72322</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>1.77624</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>1.14976</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>1.44301</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>1.65739</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>1.4245</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>1.5893</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>1.18331</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>1.62641</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>1.60565</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>1.64754</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>1.64936</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39832</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.81316</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.76903</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.80864</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.8190599999999999</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.3695</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37511</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.27097</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.5002099999999999</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.38844</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.37048</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.36768</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.35524</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34993</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.35911</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.76048</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.35944</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.34959</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.43977</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.43964</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.37973</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.37971</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.35892</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.35983</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.35903</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.36067</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.36701</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.3589</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.35732</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.38084</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.35959</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.37295</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.50008</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.37698</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.35566</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.34987</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.35838</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.34284</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.38193</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.3203</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.73015</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.42176</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.35187</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.3781</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.45653</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.58435</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.30322</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.28211</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.2976</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>1.21378</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>1.21503</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>1.14772</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.49848</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.32897</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.70097</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>1.09272</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.45206</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.30354</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.39314</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.30295</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.33588</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.29792</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.30001</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.33313</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.26798</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.30756</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.3026</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.2936</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.39351</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.39322</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.3899</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.45308</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>1.06659</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.54531</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>1.04806</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>1.05867</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>1.18261</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.38992</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>1.20149</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>1.29788</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.49941</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.43995</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>1.11747</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>1.09809</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.30018</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.29692</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.6115700000000001</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>1.17181</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.29863</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.32356</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.32637</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.32951</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.33052</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.33622</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.32708</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.33797</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.3503500000000001</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.96587</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.7305199999999999</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.728</v>
+      </c>
+      <c r="F142" t="n">
+        <v>1.49772</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.48555</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.48128</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.5192899999999999</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.5441</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.39872</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.49263</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.49271</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.52297</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.54398</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.5229400000000001</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.39324</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.38503</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.5336900000000001</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.52275</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.52288</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.523</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.52288</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.5132100000000001</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.49814</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.49819</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.49341</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.49292</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.37235</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.84801</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.50222</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.37416</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.4914</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.48441</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.48385</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.48683</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.5078</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.52696</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.38175</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>1.37279</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.5936399999999999</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.74719</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.89125</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.8783500000000001</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.87663</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.9895900000000001</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.68749</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.47701</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.42878</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.15681</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.12036</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.92187</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.26408</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.30267</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.6647799999999999</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.19576</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.47025</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.47525</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.49122</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.45628</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.46253</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.49564</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.46992</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.48902</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.28954</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.61011</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>1.62022</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>1.41779</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.47137</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.488</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.49529</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.34682</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.54665</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.5209199999999999</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.62718</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.5478999999999999</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.52383</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.37928</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.49908</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.48821</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.47508</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.6755800000000001</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.55532</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.54811</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.62617</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.5294500000000001</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.43231</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.5082300000000001</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.54001</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.53765</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.53927</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.38087</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.6514099999999999</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.5879800000000001</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.5885</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.5295</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.5299299999999999</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.53008</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.51535</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.55376</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.41962</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.5210399999999999</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.5011100000000001</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.3733</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.45963</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.45987</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.33347</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.38096</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.3503500000000001</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.3344</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.35971</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.35032</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36451</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.36088</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.43855</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.39902</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.38036</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.41204</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.49492</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.499</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.54738</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.5198200000000001</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.52012</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.51888</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.49987</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.50115</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.91307</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>1.31674</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.62127</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>1.50817</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.5178700000000001</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.5040899999999999</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.50678</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.51703</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.5033299999999999</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.50448</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.5213</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.5455399999999999</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.4975</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.50103</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.51797</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.56824</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.51854</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.51971</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.5166799999999999</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.50551</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.5185700000000001</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.50513</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.50206</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.48507</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.50459</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.51185</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.5272100000000001</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.48557</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.49033</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.50475</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.5077</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.50495</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.51381</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.5234</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.5350499999999999</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.37758</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.73349</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.83308</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.81647</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.6216799999999999</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.81548</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.76451</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.59687</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.61433</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.60894</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.65015</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.64595</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.62027</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.61613</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.7192799999999999</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.67833</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.82757</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.70382</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.60798</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.53089</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.5123799999999999</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.40856</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.40972</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38405</v>
       </c>
     </row>
   </sheetData>
